--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -3702,7 +3702,7 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -3702,7 +3702,7 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>11º e 12º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1679,25 +1679,25 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>46296</v>
+        <v>46323</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1709,20 +1709,20 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>46318</v>
+        <v>46331</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>46323</v>
+        <v>46332</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46302</v>
+        <v>46322</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46318</v>
+        <v>46330</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2369,25 +2369,25 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46322</v>
+        <v>46331</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46330</v>
+        <v>46332</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2549,25 +2549,25 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46296</v>
+        <v>46330</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2579,20 +2579,20 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46318</v>
+        <v>46331</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -2613,21 +2613,21 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46330</v>
+        <v>46332</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>46345</v>
+        <v>46350</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">

--- a/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
+++ b/Horario desenvolvido/Provas_por_Professor_Proposta_3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Provas por professor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas por professor'!$A$2:$F$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -642,42 +642,42 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>46259</v>
+        <v>46324</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -693,11 +693,11 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>46268</v>
+        <v>46259</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -723,21 +723,21 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>46304</v>
+        <v>46268</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -753,37 +753,37 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>46331</v>
+        <v>46304</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>46268</v>
+        <v>46331</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
@@ -792,12 +792,12 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -813,11 +813,11 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>46331</v>
+        <v>46269</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -873,11 +873,11 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -887,27 +887,27 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>46279</v>
+        <v>46332</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>46317</v>
+        <v>46280</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>46336</v>
+        <v>46317</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1062,42 +1062,42 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>46265</v>
+        <v>46336</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>46314</v>
+        <v>46265</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>46258</v>
+        <v>46314</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>46314</v>
+        <v>46258</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46279</v>
+        <v>46314</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -1233,21 +1233,21 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1263,21 +1263,21 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>46336</v>
+        <v>46281</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>46350</v>
+        <v>46336</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -1302,19 +1302,19 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>46282</v>
+        <v>46350</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -1353,16 +1353,16 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>46336</v>
+        <v>46282</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -1374,30 +1374,30 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>46269</v>
+        <v>46336</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>3º e 4º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>3º e 4º tempos</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -1443,11 +1443,11 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1473,21 +1473,21 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46321</v>
+        <v>46280</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>46335</v>
+        <v>46321</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>46350</v>
+        <v>46322</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
@@ -1542,37 +1542,37 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>46266</v>
+        <v>46335</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -1584,25 +1584,25 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>46274</v>
+        <v>46350</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -1619,20 +1619,20 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -1649,20 +1649,20 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
@@ -1683,21 +1683,21 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>46323</v>
+        <v>46279</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -1713,21 +1713,21 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>46331</v>
+        <v>46286</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>46332</v>
+        <v>46323</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -1773,46 +1773,46 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>46337</v>
+        <v>46331</v>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>46261</v>
+        <v>46332</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -1824,20 +1824,20 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>46282</v>
+        <v>46337</v>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>46324</v>
+        <v>46261</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>46345</v>
+        <v>46282</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -1914,20 +1914,20 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Car (Carina Campagnani)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>46302</v>
+        <v>46324</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1937,23 +1937,23 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>46289</v>
+        <v>46345</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
@@ -1962,42 +1962,42 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Car (Carina Campagnani)</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>46322</v>
+        <v>46302</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2009,20 +2009,20 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>46339</v>
+        <v>46289</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
@@ -2034,136 +2034,136 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>46275</v>
+        <v>46322</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>46344</v>
+        <v>46339</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>46304</v>
+        <v>46344</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -2184,30 +2184,30 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2219,20 +2219,20 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>46289</v>
+        <v>46274</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2279,25 +2279,25 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>46302</v>
+        <v>46279</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
@@ -2313,16 +2313,16 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>46322</v>
+        <v>46289</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
@@ -2339,11 +2339,11 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>46330</v>
+        <v>46302</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
@@ -2369,25 +2369,25 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>46331</v>
+        <v>46322</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>46332</v>
+        <v>46330</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2433,46 +2433,46 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>46339</v>
+        <v>46331</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>46266</v>
+        <v>46332</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -2484,30 +2484,30 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>46274</v>
+        <v>46339</v>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -2519,20 +2519,20 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>46330</v>
+        <v>46274</v>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
@@ -2579,20 +2579,20 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>46331</v>
+        <v>46279</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -2613,21 +2613,21 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>46332</v>
+        <v>46330</v>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2643,141 +2643,141 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>46339</v>
+        <v>46331</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>46279</v>
+        <v>46332</v>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>46336</v>
+        <v>46339</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>46330</v>
+        <v>46336</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -2793,16 +2793,16 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>46335</v>
+        <v>46276</v>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -2814,90 +2814,90 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>46258</v>
+        <v>46330</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>46275</v>
+        <v>46335</v>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -2913,11 +2913,11 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>46336</v>
+        <v>46275</v>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -2943,37 +2943,37 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>46344</v>
+        <v>46282</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>46273</v>
+        <v>46336</v>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
@@ -2987,23 +2987,23 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>46316</v>
+        <v>46344</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
@@ -3012,28 +3012,28 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>46259</v>
+        <v>46273</v>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
@@ -3054,20 +3054,20 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>46343</v>
+        <v>46316</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -3084,60 +3084,60 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>46316</v>
+        <v>46259</v>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>46318</v>
+        <v>46343</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>5º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>46323</v>
+        <v>46316</v>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>2º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3183,37 +3183,37 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>6º tempo</t>
+          <t>5º tempo</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
@@ -3222,28 +3222,28 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>9º tempo</t>
+          <t>2º tempo</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>46288</v>
+        <v>46323</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>11º tempo</t>
+          <t>6º tempo</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>1º tempo</t>
+          <t>9º tempo</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>11C1</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>46323</v>
+        <v>46288</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>11º tempo</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>10º tempo</t>
+          <t>1º tempo</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
@@ -3372,97 +3372,97 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>4º tempo</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>46259</v>
+        <v>46330</v>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>10º tempo</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>4º tempo</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>12C2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
@@ -3474,25 +3474,25 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>46314</v>
+        <v>46329</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
@@ -3504,12 +3504,12 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C102" s="9" t="n">
@@ -3522,28 +3522,28 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>46265</v>
+        <v>46314</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -3573,21 +3573,21 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>46321</v>
+        <v>46265</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>5º e 6º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>46342</v>
+        <v>46321</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
@@ -3672,19 +3672,19 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>5º e 6º tempos</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
@@ -3693,28 +3693,28 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>46276</v>
+        <v>46323</v>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -3723,97 +3723,97 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>46304</v>
+        <v>46342</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>46262</v>
+        <v>46303</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>10C2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>46269</v>
+        <v>46304</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>46314</v>
+        <v>46258</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>46332</v>
+        <v>46262</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
@@ -3882,37 +3882,37 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
@@ -3924,55 +3924,55 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>46268</v>
+        <v>46314</v>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>11C2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>46317</v>
+        <v>46332</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
@@ -3989,11 +3989,11 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>46331</v>
+        <v>46268</v>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
@@ -4002,37 +4002,37 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>9º ao 11º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -4044,20 +4044,20 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>46286</v>
+        <v>46317</v>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
@@ -4067,23 +4067,23 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>46289</v>
+        <v>46331</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
@@ -4092,12 +4092,12 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>1º e 2º tempos</t>
+          <t>9º ao 11º tempos</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>46322</v>
+        <v>46274</v>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4139,20 +4139,20 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>46323</v>
+        <v>46286</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
@@ -4169,101 +4169,101 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>46337</v>
+        <v>46289</v>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º e 2º tempos</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>46265</v>
+        <v>46322</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>46314</v>
+        <v>46323</v>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>1º ao 3º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>46274</v>
+        <v>46337</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -4272,58 +4272,58 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>6º e 7º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>46286</v>
+        <v>46314</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
@@ -4349,11 +4349,11 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46323</v>
+        <v>46274</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
@@ -4409,25 +4409,25 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>46330</v>
+        <v>46286</v>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>46337</v>
+        <v>46302</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
@@ -4452,67 +4452,67 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>46282</v>
+        <v>46323</v>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>6º e 7º tempos</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>10C1, 10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>46317</v>
+        <v>46330</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>9º e 10º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
@@ -4524,140 +4524,140 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>7º tempo</t>
+          <t>4º e 5º tempos</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>46332</v>
+        <v>46317</v>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>2º e 3º tempos</t>
+          <t>9º e 10º tempos</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>9C1, 9C2</t>
+          <t>10C1, 10C2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46273</v>
+        <v>46331</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>7º tempo</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>46329</v>
+        <v>46269</v>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
@@ -4667,14 +4667,14 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>11C1, 11C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -4683,58 +4683,58 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>46266</v>
+        <v>46332</v>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>9C1, 9C2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>46337</v>
+        <v>46273</v>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>4º e 5º tempos</t>
+          <t>10º e 11º tempos</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>46273</v>
+        <v>46329</v>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
@@ -4752,47 +4752,137 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>10º e 11º tempos</t>
+          <t>2º e 3º tempos</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>12C1, 12C2</t>
+          <t>11C1, 11C2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Ing</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F144" s="10" t="inlineStr">
+        <is>
+          <t>10C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Ing</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>46337</v>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>10C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
           <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>Hist</t>
         </is>
       </c>
-      <c r="C144" s="9" t="n">
+      <c r="C146" s="9" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="F146" s="10" t="inlineStr">
+        <is>
+          <t>12C1, 12C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Hist</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
         <v>46315</v>
       </c>
-      <c r="D144" s="10" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E144" s="10" t="inlineStr">
+      <c r="E147" s="6" t="inlineStr">
         <is>
           <t>10º e 11º tempos</t>
         </is>
       </c>
-      <c r="F144" s="10" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <t>12C1, 12C2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F144"/>
+  <autoFilter ref="A2:F147"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
